--- a/MAJEntreesCDA/ig/StructureDefinition-fr-cda-dicom-observation.xlsx
+++ b/MAJEntreesCDA/ig/StructureDefinition-fr-cda-dicom-observation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$181</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5325" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5674" uniqueCount="484">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T09:38:07+00:00</t>
+    <t>2026-04-20T13:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -526,6 +526,132 @@
     <t>http://terminology.hl7.org/ValueSet/v3-ObservationType</t>
   </si>
   <si>
+    <t>Observation.code.nullFlavor</t>
+  </si>
+  <si>
+    <t>Observation.code.code</t>
+  </si>
+  <si>
+    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
+  </si>
+  <si>
+    <t>CD.code</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystem</t>
+  </si>
+  <si>
+    <t>Code System</t>
+  </si>
+  <si>
+    <t>Specifies the code system that defines the code.</t>
+  </si>
+  <si>
+    <t>CD.codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystemName</t>
+  </si>
+  <si>
+    <t>Code System Name</t>
+  </si>
+  <si>
+    <t>The common name of the coding system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemName</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Code System Version</t>
+  </si>
+  <si>
+    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.displayName</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
+  </si>
+  <si>
+    <t>CD.displayName</t>
+  </si>
+  <si>
+    <t>Observation.code.sdtcValueSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
+</t>
+  </si>
+  <si>
+    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.valueSet</t>
+  </si>
+  <si>
+    <t>Observation.code.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.originalText</t>
+  </si>
+  <si>
+    <t>Original Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
+</t>
+  </si>
+  <si>
+    <t>The text or phrase used as the basis for the coding.</t>
+  </si>
+  <si>
+    <t>CD.originalText</t>
+  </si>
+  <si>
+    <t>Observation.code.qualifier</t>
+  </si>
+  <si>
+    <t>Qualifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
+</t>
+  </si>
+  <si>
+    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
+  </si>
+  <si>
+    <t>CD.qualifier</t>
+  </si>
+  <si>
+    <t>Observation.code.translation</t>
+  </si>
+  <si>
+    <t>Translation</t>
+  </si>
+  <si>
+    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
+  </si>
+  <si>
+    <t>CD.translation</t>
+  </si>
+  <si>
     <t>Observation.derivationExpr</t>
   </si>
   <si>
@@ -536,10 +662,6 @@
     <t>Observation.text</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
-</t>
-  </si>
-  <si>
     <t>Partie narrative de l'observation</t>
   </si>
   <si>
@@ -722,94 +844,27 @@
     <t>Observation.value.code</t>
   </si>
   <si>
-    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
-  </si>
-  <si>
-    <t>CD.code</t>
-  </si>
-  <si>
     <t>Observation.value.codeSystem</t>
   </si>
   <si>
-    <t>Code System</t>
-  </si>
-  <si>
-    <t>Specifies the code system that defines the code.</t>
-  </si>
-  <si>
-    <t>CD.codeSystem</t>
-  </si>
-  <si>
     <t>Observation.value.codeSystemName</t>
   </si>
   <si>
-    <t>Code System Name</t>
-  </si>
-  <si>
-    <t>The common name of the coding system.</t>
-  </si>
-  <si>
-    <t>CD.codeSystemName</t>
-  </si>
-  <si>
     <t>Observation.value.codeSystemVersion</t>
   </si>
   <si>
-    <t>Code System Version</t>
-  </si>
-  <si>
-    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
-  </si>
-  <si>
-    <t>CD.codeSystemVersion</t>
-  </si>
-  <si>
     <t>Observation.value.displayName</t>
   </si>
   <si>
-    <t>Display Name</t>
-  </si>
-  <si>
-    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
-  </si>
-  <si>
-    <t>CD.displayName</t>
-  </si>
-  <si>
     <t>Observation.value.sdtcValueSet</t>
   </si>
   <si>
-    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
-</t>
-  </si>
-  <si>
-    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
-  </si>
-  <si>
-    <t>CD.valueSet</t>
-  </si>
-  <si>
     <t>Observation.value.sdtcValueSetVersion</t>
   </si>
   <si>
-    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
-  </si>
-  <si>
-    <t>CD.sdtcValueSetVersion</t>
-  </si>
-  <si>
     <t>Observation.value.originalText</t>
   </si>
   <si>
-    <t>Original Text</t>
-  </si>
-  <si>
-    <t>The text or phrase used as the basis for the coding.</t>
-  </si>
-  <si>
-    <t>CD.originalText</t>
-  </si>
-  <si>
     <t>Observation.value.originalText.nullFlavor</t>
   </si>
   <si>
@@ -843,29 +898,7 @@
     <t>Observation.value.qualifier</t>
   </si>
   <si>
-    <t>Qualifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
-</t>
-  </si>
-  <si>
-    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
-  </si>
-  <si>
-    <t>CD.qualifier</t>
-  </si>
-  <si>
     <t>Observation.value.translation</t>
-  </si>
-  <si>
-    <t>Translation</t>
-  </si>
-  <si>
-    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
-  </si>
-  <si>
-    <t>CD.translation</t>
   </si>
   <si>
     <t>Observation.interpretationCode</t>
@@ -1798,7 +1831,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK170"/>
+  <dimension ref="A1:AK181"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="76.359375" customWidth="true" bestFit="true"/>
@@ -4499,7 +4532,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>158</v>
       </c>
@@ -4518,7 +4551,7 @@
         <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>74</v>
@@ -4813,7 +4846,9 @@
       <c r="D30" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E30" s="2"/>
+      <c r="E30" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F30" t="s" s="2">
         <v>80</v>
       </c>
@@ -4830,10 +4865,12 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>167</v>
+        <v>85</v>
       </c>
       <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
+      <c r="M30" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4859,13 +4896,11 @@
         <v>74</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>74</v>
@@ -4883,7 +4918,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>166</v>
+        <v>89</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4903,18 +4938,20 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E31" s="2"/>
+      <c r="E31" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>75</v>
@@ -4929,13 +4966,11 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4986,7 +5021,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5004,28 +5039,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>84</v>
+        <v>171</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>74</v>
@@ -5034,11 +5069,11 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5065,11 +5100,13 @@
         <v>74</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y32" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z32" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>74</v>
@@ -5087,7 +5124,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>89</v>
+        <v>173</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5107,17 +5144,17 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>80</v>
@@ -5135,11 +5172,11 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5166,11 +5203,13 @@
         <v>74</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y33" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z33" t="s" s="2">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>74</v>
@@ -5188,7 +5227,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5208,17 +5247,17 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>80</v>
@@ -5236,7 +5275,7 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>179</v>
+        <v>102</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
@@ -5309,7 +5348,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>182</v>
       </c>
@@ -5324,13 +5363,13 @@
         <v>183</v>
       </c>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>74</v>
@@ -5339,7 +5378,7 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
@@ -5370,29 +5409,31 @@
         <v>74</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5412,18 +5453,16 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E36" t="s" s="2">
-        <v>188</v>
-      </c>
+      <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
@@ -5440,11 +5479,11 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5495,7 +5534,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5515,18 +5554,16 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E37" t="s" s="2">
-        <v>192</v>
-      </c>
+      <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>80</v>
       </c>
@@ -5543,11 +5580,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5574,11 +5611,13 @@
         <v>74</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Y37" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z37" t="s" s="2">
-        <v>194</v>
+        <v>74</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>74</v>
@@ -5596,7 +5635,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5616,16 +5655,18 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E38" s="2"/>
+      <c r="E38" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
@@ -5642,10 +5683,12 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>85</v>
+        <v>195</v>
       </c>
       <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
+      <c r="M38" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5671,29 +5714,31 @@
         <v>74</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y38" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5713,21 +5758,23 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E39" s="2"/>
+      <c r="E39" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>74</v>
@@ -5739,17 +5786,13 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L39" t="s" s="2">
         <v>200</v>
       </c>
+      <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="N39" t="s" s="2">
-        <v>202</v>
-      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>74</v>
@@ -5798,46 +5841,46 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AG39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>204</v>
-      </c>
       <c r="B40" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F40" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5846,11 +5889,11 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>206</v>
+        <v>161</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5901,13 +5944,13 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>74</v>
@@ -5921,18 +5964,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E41" t="s" s="2">
-        <v>210</v>
-      </c>
+      <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
@@ -5949,12 +5990,10 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="L41" s="2"/>
-      <c r="M41" t="s" s="2">
-        <v>211</v>
-      </c>
+      <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6004,7 +6043,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6024,10 +6063,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6035,7 +6074,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>75</v>
@@ -6050,13 +6089,13 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>91</v>
+        <v>195</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6083,11 +6122,13 @@
         <v>74</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y42" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z42" t="s" s="2">
-        <v>215</v>
+        <v>74</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>74</v>
@@ -6105,7 +6146,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6123,18 +6164,20 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E43" s="2"/>
+      <c r="E43" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
@@ -6142,7 +6185,7 @@
         <v>75</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>74</v>
@@ -6151,13 +6194,11 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>218</v>
+        <v>86</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6184,13 +6225,11 @@
         <v>74</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>74</v>
@@ -6208,7 +6247,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>216</v>
+        <v>89</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6228,16 +6267,18 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E44" s="2"/>
+      <c r="E44" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
@@ -6254,10 +6295,12 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>220</v>
+        <v>85</v>
       </c>
       <c r="L44" s="2"/>
-      <c r="M44" s="2"/>
+      <c r="M44" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6283,11 +6326,11 @@
         <v>74</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>164</v>
+        <v>87</v>
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>74</v>
@@ -6305,7 +6348,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6325,16 +6368,18 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E45" s="2"/>
+      <c r="E45" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
@@ -6351,10 +6396,12 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
+      <c r="M45" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6404,7 +6451,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6424,16 +6471,18 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E46" s="2"/>
+      <c r="E46" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
@@ -6450,10 +6499,12 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L46" s="2"/>
-      <c r="M46" s="2"/>
+      <c r="M46" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6501,7 +6552,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6519,26 +6570,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E47" s="2"/>
+      <c r="E47" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="F47" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>
@@ -6547,10 +6600,12 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="L47" s="2"/>
-      <c r="M47" s="2"/>
+      <c r="M47" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6600,13 +6655,13 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>74</v>
@@ -6620,17 +6675,17 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>84</v>
+        <v>232</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>80</v>
@@ -6652,7 +6707,7 @@
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>86</v>
+        <v>233</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6679,11 +6734,11 @@
         <v>74</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>87</v>
+        <v>164</v>
       </c>
       <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>88</v>
+        <v>234</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>74</v>
@@ -6701,7 +6756,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>89</v>
+        <v>235</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6721,18 +6776,16 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E49" t="s" s="2">
-        <v>62</v>
-      </c>
+      <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
@@ -6752,9 +6805,7 @@
         <v>85</v>
       </c>
       <c r="L49" s="2"/>
-      <c r="M49" t="s" s="2">
-        <v>229</v>
-      </c>
+      <c r="M49" s="2"/>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6780,13 +6831,11 @@
         <v>74</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>74</v>
+        <v>237</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>74</v>
@@ -6804,7 +6853,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6824,18 +6873,16 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E50" t="s" s="2">
-        <v>232</v>
-      </c>
+      <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
@@ -6852,13 +6899,17 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L50" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="M50" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>74</v>
@@ -6907,7 +6958,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6925,28 +6976,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>74</v>
@@ -6955,11 +7006,11 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>102</v>
+        <v>246</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7010,7 +7061,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7030,17 +7081,17 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>80</v>
@@ -7058,11 +7109,11 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>102</v>
+        <v>195</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7113,7 +7164,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7131,28 +7182,26 @@
         <v>74</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E53" t="s" s="2">
-        <v>244</v>
-      </c>
+      <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>74</v>
@@ -7161,11 +7210,13 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L53" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="M53" t="s" s="2">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7192,13 +7243,11 @@
         <v>74</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>74</v>
+        <v>255</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>74</v>
@@ -7216,7 +7265,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -7234,12 +7283,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7253,7 +7302,7 @@
         <v>75</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>74</v>
@@ -7262,11 +7311,13 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="L54" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="M54" t="s" s="2">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7317,7 +7368,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -7337,10 +7388,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7363,12 +7414,10 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>102</v>
+        <v>260</v>
       </c>
       <c r="L55" s="2"/>
-      <c r="M55" t="s" s="2">
-        <v>252</v>
-      </c>
+      <c r="M55" s="2"/>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7394,13 +7443,11 @@
         <v>74</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>74</v>
+        <v>261</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>74</v>
@@ -7418,7 +7465,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -7436,20 +7483,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E56" t="s" s="2">
-        <v>255</v>
-      </c>
+      <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
@@ -7457,7 +7502,7 @@
         <v>75</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>74</v>
@@ -7466,12 +7511,10 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>169</v>
+        <v>263</v>
       </c>
       <c r="L56" s="2"/>
-      <c r="M56" t="s" s="2">
-        <v>256</v>
-      </c>
+      <c r="M56" s="2"/>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7521,7 +7564,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7541,18 +7584,16 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E57" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
@@ -7569,12 +7610,10 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="L57" s="2"/>
-      <c r="M57" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M57" s="2"/>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7604,7 +7643,7 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>88</v>
+        <v>265</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>74</v>
@@ -7622,7 +7661,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>89</v>
+        <v>264</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7640,28 +7679,26 @@
         <v>74</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E58" t="s" s="2">
-        <v>173</v>
-      </c>
+      <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>74</v>
@@ -7670,12 +7707,10 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="L58" s="2"/>
-      <c r="M58" t="s" s="2">
-        <v>174</v>
-      </c>
+      <c r="M58" s="2"/>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7701,11 +7736,13 @@
         <v>74</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y58" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z58" t="s" s="2">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>74</v>
@@ -7723,13 +7760,13 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>176</v>
+        <v>266</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>74</v>
@@ -7743,17 +7780,17 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>178</v>
+        <v>84</v>
       </c>
       <c r="F59" t="s" s="2">
         <v>80</v>
@@ -7771,11 +7808,11 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>179</v>
+        <v>85</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" t="s" s="2">
-        <v>180</v>
+        <v>86</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7802,13 +7839,11 @@
         <v>74</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -7826,7 +7861,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>181</v>
+        <v>89</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7846,17 +7881,17 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>183</v>
+        <v>62</v>
       </c>
       <c r="F60" t="s" s="2">
         <v>80</v>
@@ -7878,7 +7913,7 @@
       </c>
       <c r="L60" s="2"/>
       <c r="M60" t="s" s="2">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7905,11 +7940,13 @@
         <v>74</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y60" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z60" t="s" s="2">
-        <v>185</v>
+        <v>74</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>74</v>
@@ -7927,7 +7964,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7947,17 +7984,17 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="F61" t="s" s="2">
         <v>80</v>
@@ -7975,11 +8012,11 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" t="s" s="2">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8030,7 +8067,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -8050,17 +8087,17 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="F62" t="s" s="2">
         <v>80</v>
@@ -8078,11 +8115,11 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" t="s" s="2">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8109,11 +8146,13 @@
         <v>74</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Y62" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z62" t="s" s="2">
-        <v>194</v>
+        <v>74</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>74</v>
@@ -8131,7 +8170,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -8151,16 +8190,18 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E63" s="2"/>
+      <c r="E63" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
@@ -8177,10 +8218,12 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L63" s="2"/>
-      <c r="M63" s="2"/>
+      <c r="M63" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8206,11 +8249,13 @@
         <v>74</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y63" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z63" t="s" s="2">
-        <v>197</v>
+        <v>74</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>74</v>
@@ -8228,7 +8273,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -8248,16 +8293,18 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E64" s="2"/>
+      <c r="E64" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
@@ -8276,15 +8323,11 @@
       <c r="K64" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="L64" t="s" s="2">
-        <v>200</v>
-      </c>
+      <c r="L64" s="2"/>
       <c r="M64" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>74</v>
@@ -8333,7 +8376,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -8351,20 +8394,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E65" t="s" s="2">
-        <v>205</v>
-      </c>
+      <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>80</v>
       </c>
@@ -8372,7 +8413,7 @@
         <v>75</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>74</v>
@@ -8381,11 +8422,11 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" t="s" s="2">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8436,7 +8477,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8456,18 +8497,16 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E66" t="s" s="2">
-        <v>210</v>
-      </c>
+      <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>80</v>
       </c>
@@ -8484,11 +8523,11 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>169</v>
+        <v>102</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" t="s" s="2">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8539,7 +8578,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8557,28 +8596,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>269</v>
+        <v>194</v>
       </c>
       <c r="F67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>74</v>
@@ -8587,11 +8626,11 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>270</v>
+        <v>195</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" t="s" s="2">
-        <v>271</v>
+        <v>196</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8642,13 +8681,13 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>272</v>
+        <v>197</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>74</v>
@@ -8662,23 +8701,23 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>274</v>
+        <v>84</v>
       </c>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>74</v>
@@ -8690,11 +8729,11 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" t="s" s="2">
-        <v>275</v>
+        <v>86</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8721,13 +8760,11 @@
         <v>74</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>74</v>
@@ -8745,13 +8782,13 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>276</v>
+        <v>89</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>74</v>
@@ -8763,7 +8800,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
         <v>277</v>
       </c>
@@ -8774,7 +8811,9 @@
       <c r="D69" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E69" s="2"/>
+      <c r="E69" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
@@ -8782,7 +8821,7 @@
         <v>75</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>74</v>
@@ -8791,13 +8830,11 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L69" s="2"/>
       <c r="M69" t="s" s="2">
-        <v>278</v>
+        <v>214</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8828,7 +8865,7 @@
       </c>
       <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>279</v>
+        <v>215</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>74</v>
@@ -8846,13 +8883,13 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>277</v>
+        <v>216</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>74</v>
@@ -8864,18 +8901,20 @@
         <v>74</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E70" s="2"/>
+      <c r="E70" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
@@ -8883,7 +8922,7 @@
         <v>75</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>74</v>
@@ -8892,13 +8931,11 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L70" s="2"/>
+      <c r="M70" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8925,11 +8962,13 @@
         <v>74</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Y70" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z70" t="s" s="2">
-        <v>281</v>
+        <v>74</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>74</v>
@@ -8947,13 +8986,13 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>280</v>
+        <v>221</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>74</v>
@@ -8967,18 +9006,20 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E71" s="2"/>
+      <c r="E71" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="F71" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>75</v>
@@ -8993,13 +9034,11 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L71" s="2"/>
       <c r="M71" t="s" s="2">
-        <v>284</v>
+        <v>224</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9026,13 +9065,11 @@
         <v>74</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>74</v>
+        <v>225</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>74</v>
@@ -9050,13 +9087,13 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>282</v>
+        <v>226</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>74</v>
@@ -9070,17 +9107,17 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>84</v>
+        <v>228</v>
       </c>
       <c r="F72" t="s" s="2">
         <v>80</v>
@@ -9102,7 +9139,7 @@
       </c>
       <c r="L72" s="2"/>
       <c r="M72" t="s" s="2">
-        <v>86</v>
+        <v>229</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9129,11 +9166,13 @@
         <v>74</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y72" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z72" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>74</v>
@@ -9151,7 +9190,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>89</v>
+        <v>230</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -9171,17 +9210,17 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>62</v>
+        <v>232</v>
       </c>
       <c r="F73" t="s" s="2">
         <v>80</v>
@@ -9203,7 +9242,7 @@
       </c>
       <c r="L73" s="2"/>
       <c r="M73" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9230,13 +9269,11 @@
         <v>74</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>74</v>
+        <v>234</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>74</v>
@@ -9254,7 +9291,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -9274,18 +9311,16 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E74" t="s" s="2">
-        <v>232</v>
-      </c>
+      <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>80</v>
       </c>
@@ -9302,12 +9337,10 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="L74" s="2"/>
-      <c r="M74" t="s" s="2">
-        <v>233</v>
-      </c>
+      <c r="M74" s="2"/>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9333,13 +9366,11 @@
         <v>74</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>74</v>
+        <v>237</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>74</v>
@@ -9357,7 +9388,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -9377,18 +9408,16 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E75" t="s" s="2">
-        <v>236</v>
-      </c>
+      <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>80</v>
       </c>
@@ -9407,11 +9436,15 @@
       <c r="K75" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="L75" s="2"/>
+      <c r="L75" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="M75" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>74</v>
@@ -9460,7 +9493,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9478,19 +9511,19 @@
         <v>74</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E76" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F76" t="s" s="2">
         <v>80</v>
@@ -9499,7 +9532,7 @@
         <v>75</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>74</v>
@@ -9508,11 +9541,11 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>102</v>
+        <v>246</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -9563,7 +9596,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9583,17 +9616,17 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E77" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="F77" t="s" s="2">
         <v>80</v>
@@ -9611,11 +9644,11 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>102</v>
+        <v>195</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9666,7 +9699,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9686,21 +9719,23 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E78" s="2"/>
+      <c r="E78" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="F78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>74</v>
@@ -9712,11 +9747,11 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>248</v>
+        <v>200</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" t="s" s="2">
-        <v>249</v>
+        <v>201</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9767,13 +9802,13 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>250</v>
+        <v>202</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>74</v>
@@ -9787,21 +9822,23 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E79" s="2"/>
+      <c r="E79" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>74</v>
@@ -9813,11 +9850,11 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>102</v>
+        <v>161</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" t="s" s="2">
-        <v>252</v>
+        <v>205</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -9868,13 +9905,13 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>253</v>
+        <v>206</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>74</v>
@@ -9886,20 +9923,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E80" t="s" s="2">
-        <v>255</v>
-      </c>
+      <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
@@ -9907,7 +9942,7 @@
         <v>75</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>74</v>
@@ -9916,11 +9951,13 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="L80" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="M80" t="s" s="2">
-        <v>256</v>
+        <v>289</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -9947,13 +9984,11 @@
         <v>74</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>74</v>
+        <v>290</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>74</v>
@@ -9971,13 +10006,13 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>257</v>
+        <v>288</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>74</v>
@@ -9991,18 +10026,16 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E81" t="s" s="2">
-        <v>269</v>
-      </c>
+      <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>80</v>
       </c>
@@ -10019,13 +10052,13 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10052,13 +10085,11 @@
         <v>74</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
-        <v>74</v>
+        <v>292</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>74</v>
@@ -10076,7 +10107,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -10096,20 +10127,18 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E82" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>75</v>
@@ -10124,11 +10153,13 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L82" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="M82" t="s" s="2">
-        <v>86</v>
+        <v>295</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10155,11 +10186,13 @@
         <v>74</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y82" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z82" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>74</v>
@@ -10177,13 +10210,13 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>89</v>
+        <v>293</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>74</v>
@@ -10197,17 +10230,17 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>298</v>
+        <v>84</v>
       </c>
       <c r="F83" t="s" s="2">
         <v>80</v>
@@ -10225,11 +10258,11 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>299</v>
+        <v>85</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" t="s" s="2">
-        <v>300</v>
+        <v>86</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -10256,13 +10289,11 @@
         <v>74</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>74</v>
@@ -10280,7 +10311,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>301</v>
+        <v>89</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -10298,28 +10329,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E84" t="s" s="2">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="F84" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>74</v>
@@ -10328,11 +10359,11 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>303</v>
+        <v>85</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" t="s" s="2">
-        <v>304</v>
+        <v>168</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10383,7 +10414,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>305</v>
+        <v>169</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -10403,17 +10434,17 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E85" t="s" s="2">
-        <v>84</v>
+        <v>171</v>
       </c>
       <c r="F85" t="s" s="2">
         <v>80</v>
@@ -10431,11 +10462,11 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" t="s" s="2">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10462,11 +10493,13 @@
         <v>74</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y85" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z85" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>74</v>
@@ -10484,7 +10517,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>89</v>
+        <v>173</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10504,17 +10537,17 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E86" t="s" s="2">
-        <v>62</v>
+        <v>175</v>
       </c>
       <c r="F86" t="s" s="2">
         <v>80</v>
@@ -10532,11 +10565,11 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" t="s" s="2">
-        <v>229</v>
+        <v>176</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -10548,7 +10581,7 @@
         <v>74</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>308</v>
+        <v>74</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>74</v>
@@ -10587,7 +10620,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>230</v>
+        <v>177</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10607,17 +10640,17 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E87" t="s" s="2">
-        <v>232</v>
+        <v>179</v>
       </c>
       <c r="F87" t="s" s="2">
         <v>80</v>
@@ -10635,11 +10668,11 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" t="s" s="2">
-        <v>233</v>
+        <v>180</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -10651,7 +10684,7 @@
         <v>74</v>
       </c>
       <c r="S87" t="s" s="2">
-        <v>310</v>
+        <v>74</v>
       </c>
       <c r="T87" t="s" s="2">
         <v>74</v>
@@ -10690,7 +10723,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>234</v>
+        <v>181</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10710,17 +10743,17 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>236</v>
+        <v>183</v>
       </c>
       <c r="F88" t="s" s="2">
         <v>80</v>
@@ -10742,7 +10775,7 @@
       </c>
       <c r="L88" s="2"/>
       <c r="M88" t="s" s="2">
-        <v>237</v>
+        <v>184</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -10754,7 +10787,7 @@
         <v>74</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>312</v>
+        <v>74</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>74</v>
@@ -10793,7 +10826,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>238</v>
+        <v>185</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10813,18 +10846,16 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E89" t="s" s="2">
-        <v>240</v>
-      </c>
+      <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>80</v>
       </c>
@@ -10841,11 +10872,11 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>102</v>
+        <v>187</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" t="s" s="2">
-        <v>241</v>
+        <v>188</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -10896,7 +10927,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>242</v>
+        <v>189</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10916,18 +10947,16 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E90" t="s" s="2">
-        <v>244</v>
-      </c>
+      <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>80</v>
       </c>
@@ -10948,7 +10977,7 @@
       </c>
       <c r="L90" s="2"/>
       <c r="M90" t="s" s="2">
-        <v>245</v>
+        <v>191</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -10960,7 +10989,7 @@
         <v>74</v>
       </c>
       <c r="S90" t="s" s="2">
-        <v>315</v>
+        <v>74</v>
       </c>
       <c r="T90" t="s" s="2">
         <v>74</v>
@@ -10999,7 +11028,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>246</v>
+        <v>192</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -11019,16 +11048,18 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E91" s="2"/>
+      <c r="E91" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="F91" t="s" s="2">
         <v>80</v>
       </c>
@@ -11045,11 +11076,11 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>248</v>
+        <v>195</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" t="s" s="2">
-        <v>249</v>
+        <v>196</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -11100,7 +11131,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>250</v>
+        <v>197</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -11118,18 +11149,20 @@
         <v>74</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E92" s="2"/>
+      <c r="E92" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="F92" t="s" s="2">
         <v>80</v>
       </c>
@@ -11137,7 +11170,7 @@
         <v>75</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>74</v>
@@ -11146,11 +11179,13 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L92" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="M92" t="s" s="2">
-        <v>252</v>
+        <v>306</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -11201,13 +11236,13 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>253</v>
+        <v>202</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>74</v>
@@ -11221,17 +11256,17 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E93" t="s" s="2">
-        <v>255</v>
+        <v>84</v>
       </c>
       <c r="F93" t="s" s="2">
         <v>80</v>
@@ -11249,11 +11284,11 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" t="s" s="2">
-        <v>256</v>
+        <v>86</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -11280,13 +11315,11 @@
         <v>74</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>74</v>
@@ -11304,7 +11337,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>257</v>
+        <v>89</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -11324,23 +11357,23 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E94" t="s" s="2">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="F94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>74</v>
@@ -11352,11 +11385,11 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>270</v>
+        <v>310</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" t="s" s="2">
-        <v>271</v>
+        <v>311</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -11407,13 +11440,13 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>272</v>
+        <v>312</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>74</v>
@@ -11425,28 +11458,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E95" t="s" s="2">
-        <v>274</v>
+        <v>6</v>
       </c>
       <c r="F95" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>74</v>
@@ -11455,11 +11488,11 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>161</v>
+        <v>314</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" t="s" s="2">
-        <v>275</v>
+        <v>315</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -11510,13 +11543,13 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>276</v>
+        <v>316</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>74</v>
@@ -11528,28 +11561,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E96" t="s" s="2">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="F96" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>74</v>
@@ -11558,13 +11591,11 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L96" s="2"/>
       <c r="M96" t="s" s="2">
-        <v>322</v>
+        <v>86</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -11595,7 +11626,7 @@
       </c>
       <c r="Y96" s="2"/>
       <c r="Z96" t="s" s="2">
-        <v>323</v>
+        <v>88</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>74</v>
@@ -11613,7 +11644,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>324</v>
+        <v>89</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11633,23 +11664,23 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E97" t="s" s="2">
-        <v>274</v>
+        <v>62</v>
       </c>
       <c r="F97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>74</v>
@@ -11661,11 +11692,11 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="L97" s="2"/>
       <c r="M97" t="s" s="2">
-        <v>275</v>
+        <v>168</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -11677,7 +11708,7 @@
         <v>74</v>
       </c>
       <c r="S97" t="s" s="2">
-        <v>74</v>
+        <v>319</v>
       </c>
       <c r="T97" t="s" s="2">
         <v>74</v>
@@ -11716,13 +11747,13 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>276</v>
+        <v>169</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>74</v>
@@ -11736,16 +11767,18 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E98" s="2"/>
+      <c r="E98" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="F98" t="s" s="2">
         <v>80</v>
       </c>
@@ -11762,10 +11795,12 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>327</v>
+        <v>112</v>
       </c>
       <c r="L98" s="2"/>
-      <c r="M98" s="2"/>
+      <c r="M98" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -11776,7 +11811,7 @@
         <v>74</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>74</v>
+        <v>321</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>74</v>
@@ -11815,7 +11850,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>326</v>
+        <v>173</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -11835,21 +11870,23 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E99" s="2"/>
+      <c r="E99" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="F99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>74</v>
@@ -11861,10 +11898,12 @@
         <v>74</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>329</v>
+        <v>102</v>
       </c>
       <c r="L99" s="2"/>
-      <c r="M99" s="2"/>
+      <c r="M99" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -11875,7 +11914,7 @@
         <v>74</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>74</v>
+        <v>323</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>74</v>
@@ -11914,13 +11953,13 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>328</v>
+        <v>177</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>74</v>
@@ -11934,21 +11973,23 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E100" s="2"/>
+      <c r="E100" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="F100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>74</v>
@@ -11960,10 +12001,12 @@
         <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>331</v>
+        <v>102</v>
       </c>
       <c r="L100" s="2"/>
-      <c r="M100" s="2"/>
+      <c r="M100" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -12013,13 +12056,13 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>330</v>
+        <v>181</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>74</v>
@@ -12033,21 +12076,23 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E101" s="2"/>
+      <c r="E101" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="F101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>74</v>
@@ -12059,10 +12104,12 @@
         <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>333</v>
+        <v>102</v>
       </c>
       <c r="L101" s="2"/>
-      <c r="M101" s="2"/>
+      <c r="M101" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -12073,7 +12120,7 @@
         <v>74</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>74</v>
+        <v>326</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>74</v>
@@ -12112,13 +12159,13 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>332</v>
+        <v>185</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>74</v>
@@ -12132,10 +12179,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12146,7 +12193,7 @@
         <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>74</v>
@@ -12158,10 +12205,12 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>335</v>
+        <v>187</v>
       </c>
       <c r="L102" s="2"/>
-      <c r="M102" s="2"/>
+      <c r="M102" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -12211,13 +12260,13 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>334</v>
+        <v>189</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>74</v>
@@ -12231,10 +12280,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12245,7 +12294,7 @@
         <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>74</v>
@@ -12257,10 +12306,12 @@
         <v>74</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>337</v>
+        <v>102</v>
       </c>
       <c r="L103" s="2"/>
-      <c r="M103" s="2"/>
+      <c r="M103" t="s" s="2">
+        <v>191</v>
+      </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -12310,13 +12361,13 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>336</v>
+        <v>192</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>74</v>
@@ -12330,24 +12381,26 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E104" s="2"/>
+      <c r="E104" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="F104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>74</v>
@@ -12356,10 +12409,12 @@
         <v>74</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>339</v>
+        <v>195</v>
       </c>
       <c r="L104" s="2"/>
-      <c r="M104" s="2"/>
+      <c r="M104" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -12397,23 +12452,25 @@
         <v>74</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="AC104" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AD104" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>338</v>
+        <v>197</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>74</v>
@@ -12427,23 +12484,23 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="C105" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E105" s="2"/>
+      <c r="E105" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="F105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>74</v>
@@ -12455,10 +12512,12 @@
         <v>74</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>339</v>
+        <v>200</v>
       </c>
       <c r="L105" s="2"/>
-      <c r="M105" s="2"/>
+      <c r="M105" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -12508,7 +12567,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>338</v>
+        <v>202</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12528,23 +12587,23 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E106" t="s" s="2">
-        <v>84</v>
+        <v>204</v>
       </c>
       <c r="F106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>74</v>
@@ -12556,11 +12615,11 @@
         <v>74</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="L106" s="2"/>
       <c r="M106" t="s" s="2">
-        <v>86</v>
+        <v>205</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -12587,11 +12646,13 @@
         <v>74</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y106" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z106" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>74</v>
@@ -12609,13 +12670,13 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>89</v>
+        <v>206</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>74</v>
@@ -12627,26 +12688,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="107" hidden="true">
+    <row r="107">
       <c r="A107" t="s" s="2">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E107" s="2"/>
+      <c r="E107" t="s" s="2">
+        <v>1</v>
+      </c>
       <c r="F107" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>74</v>
@@ -12655,11 +12718,13 @@
         <v>74</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="L107" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="M107" t="s" s="2">
-        <v>92</v>
+        <v>333</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -12686,13 +12751,11 @@
         <v>74</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>74</v>
+        <v>334</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>74</v>
@@ -12710,13 +12773,13 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>93</v>
+        <v>335</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>74</v>
@@ -12730,21 +12793,23 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E108" s="2"/>
+      <c r="E108" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="F108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>74</v>
@@ -12756,11 +12821,11 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" t="s" s="2">
-        <v>96</v>
+        <v>205</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -12811,19 +12876,19 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>97</v>
+        <v>206</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>74</v>
@@ -12831,18 +12896,16 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E109" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>80</v>
       </c>
@@ -12859,12 +12922,10 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>85</v>
+        <v>338</v>
       </c>
       <c r="L109" s="2"/>
-      <c r="M109" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M109" s="2"/>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -12890,11 +12951,13 @@
         <v>74</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y109" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z109" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>74</v>
@@ -12912,7 +12975,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>89</v>
+        <v>337</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -12932,23 +12995,21 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E110" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>74</v>
@@ -12960,12 +13021,10 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>102</v>
+        <v>340</v>
       </c>
       <c r="L110" s="2"/>
-      <c r="M110" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M110" s="2"/>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -13015,13 +13074,13 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>104</v>
+        <v>339</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>74</v>
@@ -13035,23 +13094,21 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E111" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>74</v>
@@ -13063,12 +13120,10 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>107</v>
+        <v>342</v>
       </c>
       <c r="L111" s="2"/>
-      <c r="M111" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M111" s="2"/>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -13118,13 +13173,13 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>109</v>
+        <v>341</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>74</v>
@@ -13138,23 +13193,21 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E112" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>74</v>
@@ -13166,12 +13219,10 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>112</v>
+        <v>344</v>
       </c>
       <c r="L112" s="2"/>
-      <c r="M112" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M112" s="2"/>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -13179,7 +13230,7 @@
       </c>
       <c r="Q112" s="2"/>
       <c r="R112" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S112" t="s" s="2">
         <v>74</v>
@@ -13221,13 +13272,13 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>115</v>
+        <v>343</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>74</v>
@@ -13241,23 +13292,21 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E113" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>74</v>
@@ -13269,12 +13318,10 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>102</v>
+        <v>346</v>
       </c>
       <c r="L113" s="2"/>
-      <c r="M113" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M113" s="2"/>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -13324,13 +13371,13 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>119</v>
+        <v>345</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>74</v>
@@ -13344,10 +13391,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13370,12 +13417,10 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>95</v>
+        <v>348</v>
       </c>
       <c r="L114" s="2"/>
-      <c r="M114" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M114" s="2"/>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -13425,7 +13470,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>125</v>
+        <v>347</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13445,10 +13490,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13456,13 +13501,13 @@
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>74</v>
@@ -13471,7 +13516,7 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>85</v>
+        <v>350</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
@@ -13485,7 +13530,7 @@
         <v>74</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>363</v>
+        <v>74</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>74</v>
@@ -13500,35 +13545,35 @@
         <v>74</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y115" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z115" t="s" s="2">
-        <v>364</v>
+        <v>74</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="AC115" s="2"/>
       <c r="AD115" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>74</v>
@@ -13542,12 +13587,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C116" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="C116" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="D116" t="s" s="2">
         <v>74</v>
       </c>
@@ -13556,7 +13603,7 @@
         <v>80</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>74</v>
@@ -13568,12 +13615,10 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>107</v>
+        <v>350</v>
       </c>
       <c r="L116" s="2"/>
-      <c r="M116" t="s" s="2">
-        <v>368</v>
-      </c>
+      <c r="M116" s="2"/>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -13623,13 +13668,13 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>74</v>
@@ -13643,16 +13688,18 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>370</v>
+        <v>354</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E117" s="2"/>
+      <c r="E117" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F117" t="s" s="2">
         <v>80</v>
       </c>
@@ -13669,16 +13716,16 @@
         <v>74</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L117" s="2"/>
       <c r="M117" t="s" s="2">
-        <v>372</v>
+        <v>86</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
-        <v>157</v>
+        <v>74</v>
       </c>
       <c r="Q117" s="2"/>
       <c r="R117" t="s" s="2">
@@ -13700,13 +13747,11 @@
         <v>74</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y117" s="2"/>
       <c r="Z117" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>74</v>
@@ -13724,7 +13769,7 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>373</v>
+        <v>89</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -13744,10 +13789,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13758,7 +13803,7 @@
         <v>80</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>74</v>
@@ -13770,10 +13815,12 @@
         <v>74</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="L118" s="2"/>
-      <c r="M118" s="2"/>
+      <c r="M118" t="s" s="2">
+        <v>92</v>
+      </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -13823,13 +13870,13 @@
         <v>74</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>376</v>
+        <v>93</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>74</v>
@@ -13843,10 +13890,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>377</v>
+        <v>358</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>378</v>
+        <v>359</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13869,10 +13916,12 @@
         <v>74</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>379</v>
+        <v>95</v>
       </c>
       <c r="L119" s="2"/>
-      <c r="M119" s="2"/>
+      <c r="M119" t="s" s="2">
+        <v>96</v>
+      </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -13922,7 +13971,7 @@
         <v>74</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>380</v>
+        <v>97</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -13934,7 +13983,7 @@
         <v>74</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>74</v>
@@ -13942,16 +13991,18 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>381</v>
+        <v>360</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>382</v>
+        <v>361</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E120" s="2"/>
+      <c r="E120" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F120" t="s" s="2">
         <v>80</v>
       </c>
@@ -13968,10 +14019,12 @@
         <v>74</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>383</v>
+        <v>85</v>
       </c>
       <c r="L120" s="2"/>
-      <c r="M120" s="2"/>
+      <c r="M120" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -13997,13 +14050,11 @@
         <v>74</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y120" s="2"/>
       <c r="Z120" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>74</v>
@@ -14021,7 +14072,7 @@
         <v>74</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>384</v>
+        <v>89</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -14041,16 +14092,18 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>385</v>
+        <v>362</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E121" s="2"/>
+      <c r="E121" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="F121" t="s" s="2">
         <v>80</v>
       </c>
@@ -14067,10 +14120,12 @@
         <v>74</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>387</v>
+        <v>102</v>
       </c>
       <c r="L121" s="2"/>
-      <c r="M121" s="2"/>
+      <c r="M121" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -14120,7 +14175,7 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>388</v>
+        <v>104</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -14140,16 +14195,18 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>389</v>
+        <v>364</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>390</v>
+        <v>365</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E122" s="2"/>
+      <c r="E122" t="s" s="2">
+        <v>106</v>
+      </c>
       <c r="F122" t="s" s="2">
         <v>80</v>
       </c>
@@ -14166,10 +14223,12 @@
         <v>74</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>391</v>
+        <v>107</v>
       </c>
       <c r="L122" s="2"/>
-      <c r="M122" s="2"/>
+      <c r="M122" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -14219,7 +14278,7 @@
         <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>392</v>
+        <v>109</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -14239,18 +14298,20 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>393</v>
+        <v>366</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>394</v>
+        <v>367</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E123" s="2"/>
+      <c r="E123" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="F123" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G123" t="s" s="2">
         <v>75</v>
@@ -14265,10 +14326,12 @@
         <v>74</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>395</v>
+        <v>112</v>
       </c>
       <c r="L123" s="2"/>
-      <c r="M123" s="2"/>
+      <c r="M123" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -14276,7 +14339,7 @@
       </c>
       <c r="Q123" s="2"/>
       <c r="R123" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S123" t="s" s="2">
         <v>74</v>
@@ -14318,7 +14381,7 @@
         <v>74</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>396</v>
+        <v>115</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -14338,18 +14401,20 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>397</v>
+        <v>368</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>398</v>
+        <v>369</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E124" s="2"/>
+      <c r="E124" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F124" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G124" t="s" s="2">
         <v>75</v>
@@ -14364,10 +14429,12 @@
         <v>74</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>399</v>
+        <v>102</v>
       </c>
       <c r="L124" s="2"/>
-      <c r="M124" s="2"/>
+      <c r="M124" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -14417,7 +14484,7 @@
         <v>74</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>400</v>
+        <v>119</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -14437,10 +14504,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>401</v>
+        <v>370</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>402</v>
+        <v>371</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14451,7 +14518,7 @@
         <v>80</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>74</v>
@@ -14463,10 +14530,12 @@
         <v>74</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>403</v>
+        <v>95</v>
       </c>
       <c r="L125" s="2"/>
-      <c r="M125" s="2"/>
+      <c r="M125" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -14516,13 +14585,13 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>404</v>
+        <v>125</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>74</v>
@@ -14536,10 +14605,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>405</v>
+        <v>372</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>406</v>
+        <v>373</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14547,7 +14616,7 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G126" t="s" s="2">
         <v>75</v>
@@ -14562,7 +14631,7 @@
         <v>74</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>407</v>
+        <v>85</v>
       </c>
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
@@ -14576,7 +14645,7 @@
         <v>74</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>74</v>
+        <v>374</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>74</v>
@@ -14591,13 +14660,11 @@
         <v>74</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y126" s="2"/>
       <c r="Z126" t="s" s="2">
-        <v>74</v>
+        <v>375</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>74</v>
@@ -14615,10 +14682,10 @@
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>408</v>
+        <v>376</v>
       </c>
       <c r="AG126" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH126" t="s" s="2">
         <v>75</v>
@@ -14635,10 +14702,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>409</v>
+        <v>377</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>410</v>
+        <v>378</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14661,10 +14728,12 @@
         <v>74</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>411</v>
+        <v>107</v>
       </c>
       <c r="L127" s="2"/>
-      <c r="M127" s="2"/>
+      <c r="M127" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -14714,7 +14783,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>412</v>
+        <v>380</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -14734,10 +14803,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>413</v>
+        <v>381</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>414</v>
+        <v>382</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14760,14 +14829,16 @@
         <v>74</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>415</v>
+        <v>107</v>
       </c>
       <c r="L128" s="2"/>
-      <c r="M128" s="2"/>
+      <c r="M128" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
-        <v>74</v>
+        <v>157</v>
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
@@ -14813,7 +14884,7 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>416</v>
+        <v>384</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -14833,10 +14904,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>417</v>
+        <v>385</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>418</v>
+        <v>386</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14859,7 +14930,7 @@
         <v>74</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>419</v>
+        <v>107</v>
       </c>
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
@@ -14912,7 +14983,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>420</v>
+        <v>387</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -14932,14 +15003,12 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="C130" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
         <v>74</v>
       </c>
@@ -14948,7 +15017,7 @@
         <v>80</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>74</v>
@@ -14960,7 +15029,7 @@
         <v>74</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>339</v>
+        <v>390</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
@@ -15013,13 +15082,13 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>338</v>
+        <v>391</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>74</v>
@@ -15033,18 +15102,16 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>423</v>
+        <v>392</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>344</v>
+        <v>393</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E131" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
         <v>80</v>
       </c>
@@ -15061,12 +15128,10 @@
         <v>74</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>85</v>
+        <v>394</v>
       </c>
       <c r="L131" s="2"/>
-      <c r="M131" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M131" s="2"/>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -15092,11 +15157,13 @@
         <v>74</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y131" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z131" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>74</v>
@@ -15114,7 +15181,7 @@
         <v>74</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>89</v>
+        <v>395</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -15134,10 +15201,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>424</v>
+        <v>396</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>346</v>
+        <v>397</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15148,7 +15215,7 @@
         <v>80</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>74</v>
@@ -15160,12 +15227,10 @@
         <v>74</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>91</v>
+        <v>398</v>
       </c>
       <c r="L132" s="2"/>
-      <c r="M132" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="M132" s="2"/>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -15215,13 +15280,13 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>93</v>
+        <v>399</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>74</v>
@@ -15235,10 +15300,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>425</v>
+        <v>400</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>348</v>
+        <v>401</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15261,12 +15326,10 @@
         <v>74</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>95</v>
+        <v>402</v>
       </c>
       <c r="L133" s="2"/>
-      <c r="M133" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="M133" s="2"/>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -15316,7 +15379,7 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>97</v>
+        <v>403</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -15328,7 +15391,7 @@
         <v>74</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>74</v>
@@ -15336,18 +15399,16 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>426</v>
+        <v>404</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>350</v>
+        <v>405</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E134" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
         <v>80</v>
       </c>
@@ -15364,12 +15425,10 @@
         <v>74</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>85</v>
+        <v>406</v>
       </c>
       <c r="L134" s="2"/>
-      <c r="M134" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M134" s="2"/>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -15395,11 +15454,13 @@
         <v>74</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y134" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z134" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>74</v>
@@ -15417,7 +15478,7 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>89</v>
+        <v>407</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -15437,18 +15498,16 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>427</v>
+        <v>408</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>352</v>
+        <v>409</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E135" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
         <v>80</v>
       </c>
@@ -15465,12 +15524,10 @@
         <v>74</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>102</v>
+        <v>410</v>
       </c>
       <c r="L135" s="2"/>
-      <c r="M135" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M135" s="2"/>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -15520,7 +15577,7 @@
         <v>74</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>104</v>
+        <v>411</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -15540,18 +15597,16 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>354</v>
+        <v>413</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E136" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
         <v>80</v>
       </c>
@@ -15568,12 +15623,10 @@
         <v>74</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>107</v>
+        <v>414</v>
       </c>
       <c r="L136" s="2"/>
-      <c r="M136" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M136" s="2"/>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -15623,7 +15676,7 @@
         <v>74</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>109</v>
+        <v>415</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -15643,20 +15696,18 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>356</v>
+        <v>417</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E137" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G137" t="s" s="2">
         <v>75</v>
@@ -15671,12 +15722,10 @@
         <v>74</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>112</v>
+        <v>418</v>
       </c>
       <c r="L137" s="2"/>
-      <c r="M137" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M137" s="2"/>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -15684,7 +15733,7 @@
       </c>
       <c r="Q137" s="2"/>
       <c r="R137" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S137" t="s" s="2">
         <v>74</v>
@@ -15726,7 +15775,7 @@
         <v>74</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>115</v>
+        <v>419</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -15746,20 +15795,18 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>358</v>
+        <v>421</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E138" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G138" t="s" s="2">
         <v>75</v>
@@ -15774,12 +15821,10 @@
         <v>74</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>102</v>
+        <v>422</v>
       </c>
       <c r="L138" s="2"/>
-      <c r="M138" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M138" s="2"/>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -15829,7 +15874,7 @@
         <v>74</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>119</v>
+        <v>423</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -15849,10 +15894,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>360</v>
+        <v>425</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -15863,7 +15908,7 @@
         <v>80</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>74</v>
@@ -15875,12 +15920,10 @@
         <v>74</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>95</v>
+        <v>426</v>
       </c>
       <c r="L139" s="2"/>
-      <c r="M139" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M139" s="2"/>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -15930,13 +15973,13 @@
         <v>74</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>125</v>
+        <v>427</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>74</v>
@@ -15950,10 +15993,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>362</v>
+        <v>429</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -15961,7 +16004,7 @@
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G140" t="s" s="2">
         <v>75</v>
@@ -15976,7 +16019,7 @@
         <v>74</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>85</v>
+        <v>430</v>
       </c>
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
@@ -15990,7 +16033,7 @@
         <v>74</v>
       </c>
       <c r="S140" t="s" s="2">
-        <v>363</v>
+        <v>74</v>
       </c>
       <c r="T140" t="s" s="2">
         <v>74</v>
@@ -16005,11 +16048,13 @@
         <v>74</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y140" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z140" t="s" s="2">
-        <v>364</v>
+        <v>74</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>74</v>
@@ -16027,10 +16072,10 @@
         <v>74</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>365</v>
+        <v>431</v>
       </c>
       <c r="AG140" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH140" t="s" s="2">
         <v>75</v>
@@ -16047,12 +16092,14 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="C141" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="B141" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
         <v>74</v>
       </c>
@@ -16061,7 +16108,7 @@
         <v>80</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>74</v>
@@ -16073,12 +16120,10 @@
         <v>74</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>107</v>
+        <v>350</v>
       </c>
       <c r="L141" s="2"/>
-      <c r="M141" t="s" s="2">
-        <v>368</v>
-      </c>
+      <c r="M141" s="2"/>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -16128,13 +16173,13 @@
         <v>74</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>74</v>
@@ -16151,13 +16196,15 @@
         <v>434</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E142" s="2"/>
+      <c r="E142" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F142" t="s" s="2">
         <v>80</v>
       </c>
@@ -16174,16 +16221,16 @@
         <v>74</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L142" s="2"/>
       <c r="M142" t="s" s="2">
-        <v>372</v>
+        <v>86</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
-        <v>157</v>
+        <v>74</v>
       </c>
       <c r="Q142" s="2"/>
       <c r="R142" t="s" s="2">
@@ -16205,13 +16252,11 @@
         <v>74</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y142" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y142" s="2"/>
       <c r="Z142" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>74</v>
@@ -16229,7 +16274,7 @@
         <v>74</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>373</v>
+        <v>89</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -16252,7 +16297,7 @@
         <v>435</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16263,7 +16308,7 @@
         <v>80</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>74</v>
@@ -16275,10 +16320,12 @@
         <v>74</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="L143" s="2"/>
-      <c r="M143" s="2"/>
+      <c r="M143" t="s" s="2">
+        <v>92</v>
+      </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -16328,13 +16375,13 @@
         <v>74</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>376</v>
+        <v>93</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>74</v>
@@ -16351,7 +16398,7 @@
         <v>436</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>378</v>
+        <v>359</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16374,10 +16421,12 @@
         <v>74</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>379</v>
+        <v>95</v>
       </c>
       <c r="L144" s="2"/>
-      <c r="M144" s="2"/>
+      <c r="M144" t="s" s="2">
+        <v>96</v>
+      </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -16427,7 +16476,7 @@
         <v>74</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>380</v>
+        <v>97</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -16439,7 +16488,7 @@
         <v>74</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK144" t="s" s="2">
         <v>74</v>
@@ -16450,13 +16499,15 @@
         <v>437</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>382</v>
+        <v>361</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E145" s="2"/>
+      <c r="E145" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F145" t="s" s="2">
         <v>80</v>
       </c>
@@ -16473,10 +16524,12 @@
         <v>74</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>383</v>
+        <v>85</v>
       </c>
       <c r="L145" s="2"/>
-      <c r="M145" s="2"/>
+      <c r="M145" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -16502,13 +16555,11 @@
         <v>74</v>
       </c>
       <c r="X145" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y145" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y145" s="2"/>
       <c r="Z145" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>74</v>
@@ -16526,7 +16577,7 @@
         <v>74</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>384</v>
+        <v>89</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -16549,13 +16600,15 @@
         <v>438</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E146" s="2"/>
+      <c r="E146" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="F146" t="s" s="2">
         <v>80</v>
       </c>
@@ -16572,10 +16625,12 @@
         <v>74</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>387</v>
+        <v>102</v>
       </c>
       <c r="L146" s="2"/>
-      <c r="M146" s="2"/>
+      <c r="M146" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -16625,7 +16680,7 @@
         <v>74</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>388</v>
+        <v>104</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -16648,13 +16703,15 @@
         <v>439</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>390</v>
+        <v>365</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E147" s="2"/>
+      <c r="E147" t="s" s="2">
+        <v>106</v>
+      </c>
       <c r="F147" t="s" s="2">
         <v>80</v>
       </c>
@@ -16671,10 +16728,12 @@
         <v>74</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>391</v>
+        <v>107</v>
       </c>
       <c r="L147" s="2"/>
-      <c r="M147" s="2"/>
+      <c r="M147" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -16724,7 +16783,7 @@
         <v>74</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>392</v>
+        <v>109</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -16747,15 +16806,17 @@
         <v>440</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>394</v>
+        <v>367</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E148" s="2"/>
+      <c r="E148" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="F148" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G148" t="s" s="2">
         <v>75</v>
@@ -16770,10 +16831,12 @@
         <v>74</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>441</v>
+        <v>112</v>
       </c>
       <c r="L148" s="2"/>
-      <c r="M148" s="2"/>
+      <c r="M148" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -16781,7 +16844,7 @@
       </c>
       <c r="Q148" s="2"/>
       <c r="R148" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S148" t="s" s="2">
         <v>74</v>
@@ -16823,7 +16886,7 @@
         <v>74</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>396</v>
+        <v>115</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -16843,18 +16906,20 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>398</v>
+        <v>369</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E149" s="2"/>
+      <c r="E149" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F149" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G149" t="s" s="2">
         <v>75</v>
@@ -16869,10 +16934,12 @@
         <v>74</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>399</v>
+        <v>102</v>
       </c>
       <c r="L149" s="2"/>
-      <c r="M149" s="2"/>
+      <c r="M149" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -16922,7 +16989,7 @@
         <v>74</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>400</v>
+        <v>119</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -16942,10 +17009,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>402</v>
+        <v>371</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -16956,7 +17023,7 @@
         <v>80</v>
       </c>
       <c r="G150" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H150" t="s" s="2">
         <v>74</v>
@@ -16968,10 +17035,12 @@
         <v>74</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>403</v>
+        <v>95</v>
       </c>
       <c r="L150" s="2"/>
-      <c r="M150" s="2"/>
+      <c r="M150" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -17021,13 +17090,13 @@
         <v>74</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>404</v>
+        <v>125</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI150" t="s" s="2">
         <v>74</v>
@@ -17041,10 +17110,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>406</v>
+        <v>373</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17052,7 +17121,7 @@
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G151" t="s" s="2">
         <v>75</v>
@@ -17067,7 +17136,7 @@
         <v>74</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>407</v>
+        <v>85</v>
       </c>
       <c r="L151" s="2"/>
       <c r="M151" s="2"/>
@@ -17081,7 +17150,7 @@
         <v>74</v>
       </c>
       <c r="S151" t="s" s="2">
-        <v>74</v>
+        <v>374</v>
       </c>
       <c r="T151" t="s" s="2">
         <v>74</v>
@@ -17096,13 +17165,11 @@
         <v>74</v>
       </c>
       <c r="X151" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y151" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y151" s="2"/>
       <c r="Z151" t="s" s="2">
-        <v>74</v>
+        <v>375</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>74</v>
@@ -17120,10 +17187,10 @@
         <v>74</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>408</v>
+        <v>376</v>
       </c>
       <c r="AG151" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH151" t="s" s="2">
         <v>75</v>
@@ -17140,10 +17207,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>410</v>
+        <v>378</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17166,10 +17233,12 @@
         <v>74</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>411</v>
+        <v>107</v>
       </c>
       <c r="L152" s="2"/>
-      <c r="M152" s="2"/>
+      <c r="M152" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -17219,7 +17288,7 @@
         <v>74</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>412</v>
+        <v>380</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -17239,10 +17308,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>414</v>
+        <v>382</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17265,14 +17334,16 @@
         <v>74</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>415</v>
+        <v>107</v>
       </c>
       <c r="L153" s="2"/>
-      <c r="M153" s="2"/>
+      <c r="M153" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
-        <v>74</v>
+        <v>157</v>
       </c>
       <c r="Q153" s="2"/>
       <c r="R153" t="s" s="2">
@@ -17318,7 +17389,7 @@
         <v>74</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>416</v>
+        <v>384</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -17338,10 +17409,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>418</v>
+        <v>386</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17364,7 +17435,7 @@
         <v>74</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>419</v>
+        <v>107</v>
       </c>
       <c r="L154" s="2"/>
       <c r="M154" s="2"/>
@@ -17417,7 +17488,7 @@
         <v>74</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>420</v>
+        <v>387</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -17437,10 +17508,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>448</v>
+        <v>389</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17451,7 +17522,7 @@
         <v>80</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>74</v>
@@ -17463,7 +17534,7 @@
         <v>74</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>449</v>
+        <v>390</v>
       </c>
       <c r="L155" s="2"/>
       <c r="M155" s="2"/>
@@ -17516,13 +17587,13 @@
         <v>74</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>448</v>
+        <v>391</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH155" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI155" t="s" s="2">
         <v>74</v>
@@ -17536,10 +17607,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>450</v>
+        <v>393</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -17550,7 +17621,7 @@
         <v>80</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>74</v>
@@ -17562,7 +17633,7 @@
         <v>74</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>451</v>
+        <v>394</v>
       </c>
       <c r="L156" s="2"/>
       <c r="M156" s="2"/>
@@ -17615,13 +17686,13 @@
         <v>74</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>450</v>
+        <v>395</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>74</v>
@@ -17635,10 +17706,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>452</v>
+        <v>397</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -17649,7 +17720,7 @@
         <v>80</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>74</v>
@@ -17661,7 +17732,7 @@
         <v>74</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>453</v>
+        <v>398</v>
       </c>
       <c r="L157" s="2"/>
       <c r="M157" s="2"/>
@@ -17714,13 +17785,13 @@
         <v>74</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>452</v>
+        <v>399</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI157" t="s" s="2">
         <v>74</v>
@@ -17734,10 +17805,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>454</v>
+        <v>401</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -17748,7 +17819,7 @@
         <v>80</v>
       </c>
       <c r="G158" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H158" t="s" s="2">
         <v>74</v>
@@ -17760,12 +17831,10 @@
         <v>74</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>455</v>
+        <v>402</v>
       </c>
       <c r="L158" s="2"/>
-      <c r="M158" t="s" s="2">
-        <v>456</v>
-      </c>
+      <c r="M158" s="2"/>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -17815,13 +17884,13 @@
         <v>74</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>454</v>
+        <v>403</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH158" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI158" t="s" s="2">
         <v>74</v>
@@ -17835,18 +17904,16 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>457</v>
+        <v>405</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E159" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
         <v>80</v>
       </c>
@@ -17863,12 +17930,10 @@
         <v>74</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>85</v>
+        <v>452</v>
       </c>
       <c r="L159" s="2"/>
-      <c r="M159" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M159" s="2"/>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -17894,11 +17959,13 @@
         <v>74</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y159" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y159" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z159" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>74</v>
@@ -17916,7 +17983,7 @@
         <v>74</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>89</v>
+        <v>407</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -17936,10 +18003,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>458</v>
+        <v>409</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -17950,7 +18017,7 @@
         <v>80</v>
       </c>
       <c r="G160" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H160" t="s" s="2">
         <v>74</v>
@@ -17962,12 +18029,10 @@
         <v>74</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>91</v>
+        <v>410</v>
       </c>
       <c r="L160" s="2"/>
-      <c r="M160" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="M160" s="2"/>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -18017,13 +18082,13 @@
         <v>74</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>93</v>
+        <v>411</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH160" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI160" t="s" s="2">
         <v>74</v>
@@ -18037,10 +18102,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>459</v>
+        <v>413</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18063,12 +18128,10 @@
         <v>74</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>95</v>
+        <v>414</v>
       </c>
       <c r="L161" s="2"/>
-      <c r="M161" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="M161" s="2"/>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
@@ -18118,7 +18181,7 @@
         <v>74</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>97</v>
+        <v>415</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -18130,7 +18193,7 @@
         <v>74</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK161" t="s" s="2">
         <v>74</v>
@@ -18138,18 +18201,16 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>460</v>
+        <v>417</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E162" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
         <v>80</v>
       </c>
@@ -18166,12 +18227,10 @@
         <v>74</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>85</v>
+        <v>418</v>
       </c>
       <c r="L162" s="2"/>
-      <c r="M162" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M162" s="2"/>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -18197,11 +18256,13 @@
         <v>74</v>
       </c>
       <c r="X162" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y162" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y162" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z162" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>74</v>
@@ -18219,7 +18280,7 @@
         <v>74</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>89</v>
+        <v>419</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -18239,18 +18300,16 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>461</v>
+        <v>421</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E163" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
         <v>80</v>
       </c>
@@ -18267,12 +18326,10 @@
         <v>74</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>102</v>
+        <v>422</v>
       </c>
       <c r="L163" s="2"/>
-      <c r="M163" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M163" s="2"/>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -18322,7 +18379,7 @@
         <v>74</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>104</v>
+        <v>423</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -18342,18 +18399,16 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>462</v>
+        <v>425</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E164" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
         <v>80</v>
       </c>
@@ -18370,12 +18425,10 @@
         <v>74</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>107</v>
+        <v>426</v>
       </c>
       <c r="L164" s="2"/>
-      <c r="M164" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M164" s="2"/>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -18425,7 +18478,7 @@
         <v>74</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>109</v>
+        <v>427</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -18445,20 +18498,18 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>463</v>
+        <v>429</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E165" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G165" t="s" s="2">
         <v>75</v>
@@ -18473,12 +18524,10 @@
         <v>74</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>112</v>
+        <v>430</v>
       </c>
       <c r="L165" s="2"/>
-      <c r="M165" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M165" s="2"/>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -18486,7 +18535,7 @@
       </c>
       <c r="Q165" s="2"/>
       <c r="R165" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S165" t="s" s="2">
         <v>74</v>
@@ -18528,7 +18577,7 @@
         <v>74</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>115</v>
+        <v>431</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -18548,23 +18597,21 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E166" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G166" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H166" t="s" s="2">
         <v>74</v>
@@ -18576,12 +18623,10 @@
         <v>74</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>102</v>
+        <v>460</v>
       </c>
       <c r="L166" s="2"/>
-      <c r="M166" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M166" s="2"/>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -18631,13 +18676,13 @@
         <v>74</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>119</v>
+        <v>459</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH166" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI166" t="s" s="2">
         <v>74</v>
@@ -18651,10 +18696,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -18677,12 +18722,10 @@
         <v>74</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>95</v>
+        <v>462</v>
       </c>
       <c r="L167" s="2"/>
-      <c r="M167" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M167" s="2"/>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -18732,7 +18775,7 @@
         <v>74</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>125</v>
+        <v>461</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -18752,10 +18795,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -18766,7 +18809,7 @@
         <v>80</v>
       </c>
       <c r="G168" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H168" t="s" s="2">
         <v>74</v>
@@ -18778,7 +18821,7 @@
         <v>74</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>85</v>
+        <v>464</v>
       </c>
       <c r="L168" s="2"/>
       <c r="M168" s="2"/>
@@ -18789,7 +18832,7 @@
       </c>
       <c r="Q168" s="2"/>
       <c r="R168" t="s" s="2">
-        <v>467</v>
+        <v>74</v>
       </c>
       <c r="S168" t="s" s="2">
         <v>74</v>
@@ -18807,11 +18850,13 @@
         <v>74</v>
       </c>
       <c r="X168" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y168" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y168" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z168" t="s" s="2">
-        <v>468</v>
+        <v>74</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>74</v>
@@ -18829,13 +18874,13 @@
         <v>74</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH168" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI168" t="s" s="2">
         <v>74</v>
@@ -18849,10 +18894,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -18860,10 +18905,10 @@
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G169" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H169" t="s" s="2">
         <v>74</v>
@@ -18875,10 +18920,12 @@
         <v>74</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="L169" s="2"/>
-      <c r="M169" s="2"/>
+      <c r="M169" t="s" s="2">
+        <v>467</v>
+      </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -18928,13 +18975,13 @@
         <v>74</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="AG169" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH169" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI169" t="s" s="2">
         <v>74</v>
@@ -18948,21 +18995,23 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E170" s="2"/>
+      <c r="E170" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F170" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G170" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H170" t="s" s="2">
         <v>74</v>
@@ -18974,10 +19023,12 @@
         <v>74</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>472</v>
+        <v>85</v>
       </c>
       <c r="L170" s="2"/>
-      <c r="M170" s="2"/>
+      <c r="M170" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -19003,13 +19054,11 @@
         <v>74</v>
       </c>
       <c r="X170" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y170" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y170" s="2"/>
       <c r="Z170" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>74</v>
@@ -19027,26 +19076,1137 @@
         <v>74</v>
       </c>
       <c r="AF170" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG170" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH170" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK170" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="171" hidden="true">
+      <c r="A171" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C171" s="2"/>
+      <c r="D171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E171" s="2"/>
+      <c r="F171" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K171" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L171" s="2"/>
+      <c r="M171" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N171" s="2"/>
+      <c r="O171" s="2"/>
+      <c r="P171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q171" s="2"/>
+      <c r="R171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF171" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AG171" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK171" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="172" hidden="true">
+      <c r="A172" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="B172" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C172" s="2"/>
+      <c r="D172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E172" s="2"/>
+      <c r="F172" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G172" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K172" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L172" s="2"/>
+      <c r="M172" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="N172" s="2"/>
+      <c r="O172" s="2"/>
+      <c r="P172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q172" s="2"/>
+      <c r="R172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF172" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG172" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH172" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ172" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK172" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="173" hidden="true">
+      <c r="A173" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="AG170" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH170" t="s" s="2">
+      <c r="B173" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="C173" s="2"/>
+      <c r="D173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E173" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F173" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G173" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K173" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L173" s="2"/>
+      <c r="M173" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N173" s="2"/>
+      <c r="O173" s="2"/>
+      <c r="P173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q173" s="2"/>
+      <c r="R173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X173" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y173" s="2"/>
+      <c r="Z173" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF173" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG173" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH173" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ173" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK173" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="174" hidden="true">
+      <c r="A174" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C174" s="2"/>
+      <c r="D174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E174" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F174" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K174" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L174" s="2"/>
+      <c r="M174" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N174" s="2"/>
+      <c r="O174" s="2"/>
+      <c r="P174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q174" s="2"/>
+      <c r="R174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF174" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG174" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ174" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK174" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="175" hidden="true">
+      <c r="A175" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B175" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="C175" s="2"/>
+      <c r="D175" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E175" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="F175" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G175" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H175" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I175" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J175" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K175" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L175" s="2"/>
+      <c r="M175" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N175" s="2"/>
+      <c r="O175" s="2"/>
+      <c r="P175" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q175" s="2"/>
+      <c r="R175" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S175" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T175" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U175" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V175" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W175" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X175" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y175" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z175" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA175" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB175" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC175" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD175" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE175" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF175" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG175" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH175" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI175" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ175" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK175" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="176" hidden="true">
+      <c r="A176" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="C176" s="2"/>
+      <c r="D176" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E176" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F176" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G176" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H176" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I176" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J176" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K176" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L176" s="2"/>
+      <c r="M176" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N176" s="2"/>
+      <c r="O176" s="2"/>
+      <c r="P176" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q176" s="2"/>
+      <c r="R176" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="S176" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T176" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U176" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V176" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W176" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X176" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y176" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z176" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA176" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB176" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC176" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD176" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE176" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF176" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG176" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH176" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI176" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ176" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK176" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="177" hidden="true">
+      <c r="A177" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B177" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C177" s="2"/>
+      <c r="D177" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E177" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F177" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G177" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H177" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I177" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J177" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K177" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L177" s="2"/>
+      <c r="M177" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N177" s="2"/>
+      <c r="O177" s="2"/>
+      <c r="P177" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q177" s="2"/>
+      <c r="R177" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S177" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T177" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U177" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V177" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W177" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X177" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y177" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z177" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA177" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB177" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC177" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD177" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE177" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF177" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG177" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH177" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI177" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ177" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK177" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="178" hidden="true">
+      <c r="A178" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B178" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C178" s="2"/>
+      <c r="D178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E178" s="2"/>
+      <c r="F178" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G178" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI170" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ170" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK170" t="s" s="2">
+      <c r="H178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K178" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L178" s="2"/>
+      <c r="M178" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="N178" s="2"/>
+      <c r="O178" s="2"/>
+      <c r="P178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q178" s="2"/>
+      <c r="R178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF178" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG178" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH178" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK178" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="179" hidden="true">
+      <c r="A179" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="B179" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="C179" s="2"/>
+      <c r="D179" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E179" s="2"/>
+      <c r="F179" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G179" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H179" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I179" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J179" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K179" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L179" s="2"/>
+      <c r="M179" s="2"/>
+      <c r="N179" s="2"/>
+      <c r="O179" s="2"/>
+      <c r="P179" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q179" s="2"/>
+      <c r="R179" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="S179" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T179" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U179" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V179" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W179" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X179" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y179" s="2"/>
+      <c r="Z179" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AA179" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB179" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC179" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD179" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE179" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF179" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AG179" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH179" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI179" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ179" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK179" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="180" hidden="true">
+      <c r="A180" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="B180" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="C180" s="2"/>
+      <c r="D180" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E180" s="2"/>
+      <c r="F180" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G180" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H180" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I180" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J180" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K180" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="L180" s="2"/>
+      <c r="M180" s="2"/>
+      <c r="N180" s="2"/>
+      <c r="O180" s="2"/>
+      <c r="P180" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q180" s="2"/>
+      <c r="R180" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S180" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T180" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U180" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V180" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W180" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X180" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y180" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z180" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA180" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB180" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC180" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD180" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE180" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF180" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AG180" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH180" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI180" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ180" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK180" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="181" hidden="true">
+      <c r="A181" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C181" s="2"/>
+      <c r="D181" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E181" s="2"/>
+      <c r="F181" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G181" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H181" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I181" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J181" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K181" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="L181" s="2"/>
+      <c r="M181" s="2"/>
+      <c r="N181" s="2"/>
+      <c r="O181" s="2"/>
+      <c r="P181" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q181" s="2"/>
+      <c r="R181" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S181" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T181" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U181" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V181" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W181" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X181" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y181" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z181" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA181" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB181" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC181" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD181" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE181" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF181" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AG181" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH181" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI181" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ181" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK181" t="s" s="2">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK170">
+  <autoFilter ref="A1:AK181">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -19056,7 +20216,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI169">
+  <conditionalFormatting sqref="A2:AI180">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
